--- a/verification/cases/roundtrip/comments/init.xlsx
+++ b/verification/cases/roundtrip/comments/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDBBBB7A-7C16-46AA-94F5-286C95D4869D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="880" windowWidth="25360" windowHeight="18780" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -13,8 +14,19 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet7" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -23,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -52,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -162,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A2" authorId="0">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -176,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B2" authorId="0">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -240,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D2" authorId="0">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -272,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -296,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -309,7 +321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A4" authorId="0">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -342,7 +354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -356,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C4" authorId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -375,12 +387,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -394,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -408,7 +420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -422,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0">
+    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -436,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C20" authorId="0">
+    <comment ref="C20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -450,7 +462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A21" authorId="0">
+    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -464,7 +476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C24" authorId="0">
+    <comment ref="C24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -478,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C28" authorId="0">
+    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -492,7 +504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C32" authorId="0">
+    <comment ref="C32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -511,12 +523,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -536,12 +548,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -555,10 +567,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="B2" authorId="0">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text/>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -572,7 +584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -586,7 +598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -610,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B37" authorId="0">
+    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -629,12 +641,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -648,7 +660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N34" authorId="0">
+    <comment ref="N34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -705,8 +717,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -872,6 +884,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1196,10 +1216,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
   </cols>
@@ -1276,10 +1296,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -1880,10 +1900,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet3" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -1892,27 +1912,27 @@
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="str">
-        <f>Comment(A1)</f>
-        <v>If I did this right,_x000D__x000D_This comment should be haiku:_x000D__x000D_five, seven, and five</v>
+      <c r="B1" t="e">
+        <f ca="1">Comment(A1)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="str">
-        <f>Comment(A2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="150">
+      <c r="B2" t="e">
+        <f ca="1">Comment(A2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="str">
-        <f>Comment(A1)</f>
-        <v>If I did this right,_x000D__x000D_This comment should be haiku:_x000D__x000D_five, seven, and five</v>
+      <c r="B3" s="2" t="e">
+        <f ca="1">Comment(A1)</f>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
@@ -1928,9 +1948,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1">
@@ -2310,9 +2330,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
     <row r="1" spans="1:1"/>
     <row r="34" spans="14:14"/>
